--- a/data/trans_dic/P44D-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P44D-Clase-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,25%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,84; 67,14</t>
+          <t>12,72; 67,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,7; 54,75</t>
+          <t>16,87; 55,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,61; 28,03</t>
+          <t>16,66; 28,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,89; 70,53</t>
+          <t>15,5; 70,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,97; 82,47</t>
+          <t>16,08; 79,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,96; 29,98</t>
+          <t>15,19; 29,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,54; 59,67</t>
+          <t>21,88; 62,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,31; 55,01</t>
+          <t>22,64; 56,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,27; 26,65</t>
+          <t>17,62; 27,53</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,5%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,3; 70,44</t>
+          <t>13,96; 67,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,2; 50,13</t>
+          <t>15,49; 53,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,25; 25,82</t>
+          <t>10,54; 26,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 86,97</t>
+          <t>0,0; 85,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 89,37</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,62; 23,21</t>
+          <t>8,42; 22,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,47; 63,71</t>
+          <t>19,12; 66,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,31; 49,45</t>
+          <t>14,97; 49,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,02; 22,03</t>
+          <t>11,2; 22,82</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -898,22 +898,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,1</t>
+          <t>0,0; 17,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,01; 28,87</t>
+          <t>2,97; 27,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 8,23</t>
+          <t>2,62; 12,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,52; 80,0</t>
+          <t>9,22; 74,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -923,22 +923,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 14,39</t>
+          <t>1,85; 13,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,05; 31,14</t>
+          <t>4,29; 30,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,36; 20,01</t>
+          <t>2,33; 20,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 7,21</t>
+          <t>3,06; 10,9</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,77</t>
+          <t>0,0; 13,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 5,98</t>
+          <t>0,4; 4,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,98</t>
+          <t>0,0; 26,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,99; 8,85</t>
+          <t>1,92; 8,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,42; 13,35</t>
+          <t>1,39; 13,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,69; 5,79</t>
+          <t>1,42; 5,41</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,66</t>
+          <t>0,0; 33,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,76</t>
+          <t>0,0; 2,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,54</t>
+          <t>0,0; 24,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1158,14 +1158,14 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,3</t>
+          <t>0,0; 0,95</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -1243,32 +1243,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,25</t>
+          <t>0,0; 28,08</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,12; 28,6</t>
+          <t>3,13; 29,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,11; 7,54</t>
+          <t>2,16; 7,56</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,25</t>
+          <t>0,0; 28,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,12; 28,6</t>
+          <t>3,13; 29,23</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,14; 7,73</t>
+          <t>1,97; 7,23</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,06; 22,96</t>
+          <t>6,58; 22,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,24; 20,88</t>
+          <t>9,12; 20,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,6; 10,41</t>
+          <t>7,42; 12,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,29; 27,79</t>
+          <t>10,4; 26,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,21; 19,78</t>
+          <t>6,1; 19,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,79; 9,34</t>
+          <t>5,6; 9,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,98; 21,68</t>
+          <t>9,94; 20,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,17; 17,66</t>
+          <t>9,46; 18,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,78; 9,11</t>
+          <t>7,25; 10,12</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28037</t>
+          <t>30999</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16375</t>
+          <t>18125</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>44412</t>
+          <t>49124</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3196; 13547</t>
+          <t>2566; 13571</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4850; 15904</t>
+          <t>4901; 15987</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20163; 36217</t>
+          <t>22947; 39698</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2258; 9432</t>
+          <t>2073; 9407</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1882; 9145</t>
+          <t>1783; 8778</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11022; 22084</t>
+          <t>12619; 24346</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7228; 20020</t>
+          <t>7341; 20910</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8954; 22078</t>
+          <t>9088; 22675</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>35025; 54059</t>
+          <t>38916; 60786</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14134</t>
+          <t>15502</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7557</t>
+          <t>7850</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>21691</t>
+          <t>23352</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2170; 10691</t>
+          <t>2118; 10206</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3943; 13009</t>
+          <t>4020; 13967</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8489; 21376</t>
+          <t>9058; 23073</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 6314</t>
+          <t>0; 6210</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3881</t>
+          <t>0; 4343</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4271; 11497</t>
+          <t>4674; 12355</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4369; 14295</t>
+          <t>4290; 14856</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4639; 14981</t>
+          <t>4535; 14995</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14587; 29150</t>
+          <t>15845; 32292</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5663</t>
+          <t>5944</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7041</t>
+          <t>8009</t>
         </is>
       </c>
     </row>
@@ -1965,22 +1965,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4717</t>
+          <t>0; 5067</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>902; 8666</t>
+          <t>891; 8331</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>673; 27174</t>
+          <t>2392; 11162</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1037; 8722</t>
+          <t>1006; 8108</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1990,22 +1990,22 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>161; 4688</t>
+          <t>665; 4959</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1227; 12514</t>
+          <t>1722; 12125</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>881; 7480</t>
+          <t>870; 7755</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>700; 26141</t>
+          <t>3901; 13895</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3458</t>
+          <t>3318</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4065</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>7523</t>
+          <t>7560</t>
         </is>
       </c>
     </row>
@@ -2133,12 +2133,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 6666</t>
+          <t>0; 6760</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>768; 9545</t>
+          <t>703; 7792</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 6424</t>
+          <t>0; 6109</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1700; 7568</t>
+          <t>1796; 8300</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1011; 9529</t>
+          <t>992; 9567</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4137; 14196</t>
+          <t>3797; 14483</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>396</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>396</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 9603</t>
+          <t>0; 9094</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2316,12 +2316,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 1958</t>
+          <t>0; 2921</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 9320</t>
+          <t>0; 8916</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2331,14 +2331,14 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 2326</t>
+          <t>0; 1854</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5153</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5153</t>
+          <t>5478</t>
         </is>
       </c>
     </row>
@@ -2469,32 +2469,32 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 9627</t>
+          <t>0; 9569</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1135; 10412</t>
+          <t>1139; 10640</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2538; 9079</t>
+          <t>2871; 10040</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 9627</t>
+          <t>0; 9569</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1135; 10412</t>
+          <t>1139; 10640</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2657; 9609</t>
+          <t>2689; 9886</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>51293</t>
+          <t>55763</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34918</t>
+          <t>38157</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>86210</t>
+          <t>93919</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>7959; 25874</t>
+          <t>7418; 25094</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>14556; 32903</t>
+          <t>14371; 32738</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20111; 80460</t>
+          <t>42135; 68898</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11118; 30022</t>
+          <t>11232; 28757</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6678; 21279</t>
+          <t>6564; 21009</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27372; 44155</t>
+          <t>29224; 47484</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22019; 47851</t>
+          <t>21941; 45908</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>24324; 46815</t>
+          <t>25093; 48300</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>47148; 113455</t>
+          <t>79003; 110229</t>
         </is>
       </c>
     </row>
